--- a/docs/StructureDefinition-space-blood-product.xlsx
+++ b/docs/StructureDefinition-space-blood-product.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-space-blood-product.xlsx
+++ b/docs/StructureDefinition-space-blood-product.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="268">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/space-blood-product</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/space-blood-product</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -519,7 +522,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/ValueSet/space-blood-product-vs</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/ValueSet/space-blood-product-vs</t>
   </si>
   <si>
     <t>BiologicallyDerivedProduct.status</t>
@@ -1108,54 +1111,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1193,7 +1198,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="32.94921875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="55.88671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
@@ -1210,129 +1215,129 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1340,10 +1345,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1355,16 +1360,16 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -1414,22 +1419,22 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>20</v>
@@ -1440,10 +1445,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1451,10 +1456,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1463,19 +1468,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1525,13 +1530,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1551,10 +1556,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1562,10 +1567,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1574,16 +1579,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1634,19 +1639,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1660,10 +1665,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1671,31 +1676,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1745,19 +1750,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1771,10 +1776,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1782,10 +1787,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1797,16 +1802,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1832,13 +1837,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1856,19 +1861,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1882,21 +1887,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1908,16 +1913,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1967,22 +1972,22 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AL7" t="s" s="2">
         <v>20</v>
@@ -1993,21 +1998,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2019,16 +2024,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2078,13 +2083,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2093,7 +2098,7 @@
         <v>20</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL8" t="s" s="2">
         <v>20</v>
@@ -2104,21 +2109,21 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2130,16 +2135,16 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2189,22 +2194,22 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL9" t="s" s="2">
         <v>20</v>
@@ -2215,45 +2220,45 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
@@ -2302,22 +2307,22 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>20</v>
@@ -2328,10 +2333,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2339,10 +2344,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
@@ -2351,16 +2356,16 @@
         <v>20</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2411,36 +2416,36 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2448,13 +2453,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2463,13 +2468,13 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2481,7 +2486,7 @@
         <v>20</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>20</v>
@@ -2496,13 +2501,13 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>20</v>
@@ -2520,19 +2525,19 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>20</v>
@@ -2546,10 +2551,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2557,13 +2562,13 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>20</v>
@@ -2572,13 +2577,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2605,11 +2610,11 @@
         <v>20</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>20</v>
@@ -2627,19 +2632,19 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
@@ -2653,10 +2658,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2664,10 +2669,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2679,13 +2684,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2712,13 +2717,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -2736,19 +2741,19 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
@@ -2762,10 +2767,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2773,10 +2778,10 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -2788,13 +2793,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2845,19 +2850,19 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
@@ -2871,10 +2876,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2882,10 +2887,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2897,13 +2902,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2954,19 +2959,19 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
@@ -2980,10 +2985,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2991,10 +2996,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3006,16 +3011,16 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3065,19 +3070,19 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
@@ -3091,10 +3096,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3102,13 +3107,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3117,13 +3122,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3174,19 +3179,19 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
@@ -3200,10 +3205,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3211,10 +3216,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3226,13 +3231,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3283,13 +3288,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3298,7 +3303,7 @@
         <v>20</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>20</v>
@@ -3309,21 +3314,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3335,16 +3340,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3394,22 +3399,22 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>20</v>
@@ -3420,45 +3425,45 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3507,22 +3512,22 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>20</v>
@@ -3533,10 +3538,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3544,10 +3549,10 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -3559,13 +3564,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3616,19 +3621,19 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
@@ -3642,10 +3647,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3653,13 +3658,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -3668,13 +3673,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3725,19 +3730,19 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
@@ -3751,10 +3756,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3762,13 +3767,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -3777,13 +3782,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3834,19 +3839,19 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
@@ -3860,10 +3865,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3871,13 +3876,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -3886,13 +3891,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3943,19 +3948,19 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>20</v>
@@ -3969,10 +3974,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3980,10 +3985,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -3995,13 +4000,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4052,13 +4057,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4067,7 +4072,7 @@
         <v>20</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
@@ -4078,21 +4083,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>20</v>
@@ -4104,16 +4109,16 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4163,22 +4168,22 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>20</v>
@@ -4189,45 +4194,45 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -4276,22 +4281,22 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
@@ -4302,10 +4307,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4313,13 +4318,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
@@ -4328,13 +4333,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4385,19 +4390,19 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -4411,10 +4416,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4422,13 +4427,13 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>20</v>
@@ -4437,13 +4442,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4470,13 +4475,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -4494,19 +4499,19 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -4520,10 +4525,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4531,10 +4536,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
@@ -4546,13 +4551,13 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4603,19 +4608,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -4629,10 +4634,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4640,10 +4645,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -4655,13 +4660,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4712,19 +4717,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -4738,10 +4743,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4749,10 +4754,10 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>20</v>
@@ -4764,13 +4769,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4821,19 +4826,19 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
@@ -4847,10 +4852,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4858,10 +4863,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -4873,13 +4878,13 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4930,13 +4935,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -4945,7 +4950,7 @@
         <v>20</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>20</v>
@@ -4956,21 +4961,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -4982,16 +4987,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5041,22 +5046,22 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>20</v>
@@ -5067,45 +5072,45 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5154,22 +5159,22 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>20</v>
@@ -5180,10 +5185,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5191,10 +5196,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>20</v>
@@ -5206,13 +5211,13 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5263,19 +5268,19 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
@@ -5289,10 +5294,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5300,10 +5305,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -5315,13 +5320,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5372,19 +5377,19 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -5398,10 +5403,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5409,13 +5414,13 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -5424,13 +5429,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5481,19 +5486,19 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -5507,10 +5512,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5518,10 +5523,10 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -5533,13 +5538,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5590,13 +5595,13 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
@@ -5605,7 +5610,7 @@
         <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -5616,21 +5621,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -5642,16 +5647,16 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5701,22 +5706,22 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -5727,45 +5732,45 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -5814,22 +5819,22 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -5840,10 +5845,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5851,10 +5856,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -5866,13 +5871,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5923,19 +5928,19 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
@@ -5949,10 +5954,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5960,13 +5965,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>20</v>
@@ -5975,13 +5980,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6032,19 +6037,19 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -6058,10 +6063,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6069,10 +6074,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6084,13 +6089,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6117,13 +6122,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6141,19 +6146,19 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -6167,10 +6172,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6178,13 +6183,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>20</v>
@@ -6193,13 +6198,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6250,19 +6255,19 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>20</v>
